--- a/04_번역교정/초월번역시결과물법규위반및문제소지의문구들정리.xlsx
+++ b/04_번역교정/초월번역시결과물법규위반및문제소지의문구들정리.xlsx
@@ -1,117 +1,75 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\euntaewoo\Desktop\multilingual_text_in_image_translatio_agy_sdk_uv-version\04_번역교정\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11955" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="지금까지 내용을 다시 자세히 정리해서 줘 무엇이 문제이고" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="지금까지 내용을 다시 자세히 정리해서 줘 무엇이 문제이고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="프로페셔널선블록70g_리스크개선내역" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>글로벌 크로스보더 이커머스(FDA, 약기법 등) 규제 및 뷰티 업계 표준에 맞춘 영문 상세페이지(PDP) 리스크 개선 내역</t>
-  </si>
-  <si>
-    <t>문제 소지가 있는 기존 문구</t>
-  </si>
-  <si>
-    <t>권장 대체 표현</t>
-  </si>
-  <si>
-    <t>문제점 및 수정 사유</t>
-  </si>
-  <si>
-    <t>Complex skin issues</t>
-  </si>
-  <si>
-    <t>Multiple skin concerns</t>
-  </si>
-  <si>
-    <t>복합적인 피부 고민'의 단순 직역(콩글리시). 글로벌 표준 뷰티 용어로 대체.</t>
-  </si>
-  <si>
-    <t>Troubled skin</t>
-  </si>
-  <si>
-    <t>Blemish-prone skin</t>
-  </si>
-  <si>
-    <t>북미 소비자에게 모호한 표현. 여드름성/잡티성 피부를 직관적으로 나타내는 어휘 적용.</t>
-  </si>
-  <si>
-    <t>nutrients for cellular vitality</t>
-  </si>
-  <si>
-    <t>hydration for a resilient-looking complexion</t>
-  </si>
-  <si>
-    <t>인체 구조(세포) 기능에 직접 관여한다는 뉘앙스. 의약품 오인(Drug) 리스크를 막기 위해 피부 표면 개선에 초점을 맞춤.</t>
-  </si>
-  <si>
-    <t>reinforces cellular resilience</t>
-  </si>
-  <si>
-    <t>reinforces the skin's natural moisture barrier</t>
-  </si>
-  <si>
-    <t>세포 회복력이라는 직접적 클레임을 배제하고, 화장품 기능 영역인 '피부 수분 장벽' 강화로 순화하여 규제 차단.</t>
-  </si>
-  <si>
-    <t>combats premature aging</t>
-  </si>
-  <si>
-    <t>combats the signs of premature aging</t>
-  </si>
-  <si>
-    <t>노화 자체를 막는 인체 구조적 변화가 아닌 노화 '징후' 완화로 한정하여 항노화 과장 광고 규제 방어.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="6">
     <font>
+      <name val="Arial"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <color theme="1"/>
       <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="8"/>
-      <name val="Arial"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="00334155"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F172A"/>
+        <bgColor rgb="000F172A"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -134,24 +92,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CBD5E1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CBD5E1"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="1" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -199,7 +183,7 @@
       </fill>
     </dxf>
   </dxfs>
-  <tableStyles count="1">
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="지금까지 내용을 다시 자세히 정리해서 줘 무엇이 문제이고-style" pivot="0" count="4">
       <tableStyleElement type="wholeTable" size="0" dxfId="0"/>
       <tableStyleElement type="headerRow" dxfId="3"/>
@@ -207,23 +191,79 @@
       <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A4:C9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="표1" displayName="표1" ref="A4:C9" headerRowCount="1">
   <tableColumns count="3">
     <tableColumn id="1" name="문제 소지가 있는 기존 문구"/>
     <tableColumn id="2" name="권장 대체 표현"/>
@@ -430,105 +470,415 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="34.5703125" customWidth="1"/>
-    <col min="3" max="3" width="86.5703125" customWidth="1"/>
+    <col width="24.28515625" customWidth="1" min="1" max="1"/>
+    <col width="34.5703125" customWidth="1" min="2" max="2"/>
+    <col width="86.5703125" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-    </row>
-    <row r="2" spans="1:3" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="12.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-    </row>
-    <row r="4" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>18</v>
+    <row r="1" ht="12.75" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="25.5" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>글로벌 크로스보더 이커머스(FDA, 약기법 등) 규제 및 뷰티 업계 표준에 맞춘 영문 상세페이지(PDP) 리스크 개선 내역</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="1" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>문제 소지가 있는 기존 문구</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>권장 대체 표현</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>문제점 및 수정 사유</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Complex skin issues</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Multiple skin concerns</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>복합적인 피부 고민'의 단순 직역(콩글리시). 글로벌 표준 뷰티 용어로 대체.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Troubled skin</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Blemish-prone skin</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>북미 소비자에게 모호한 표현. 여드름성/잡티성 피부를 직관적으로 나타내는 어휘 적용.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>nutrients for cellular vitality</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>hydration for a resilient-looking complexion</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>인체 구조(세포) 기능에 직접 관여한다는 뉘앙스. 의약품 오인(Drug) 리스크를 막기 위해 피부 표면 개선에 초점을 맞춤.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>reinforces cellular resilience</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>reinforces the skin's natural moisture barrier</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>세포 회복력이라는 직접적 클레임을 배제하고, 화장품 기능 영역인 '피부 수분 장벽' 강화로 순화하여 규제 차단.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>combats premature aging</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>combats the signs of premature aging</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>노화 자체를 막는 인체 구조적 변화가 아닌 노화 '징후' 완화로 한정하여 항노화 과장 광고 규제 방어.</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Logically, Skin Professional Sun Block 70g 글로벌 선스크린(FDA/MoCRA) 규제 및 뷰티 표준 리스크 개선 내역</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>위치 (이미지)</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>문제 소지가 있는 기존 문구</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>교정된 초월번역 표현</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>문제점 및 수정 사유 (MoCRA / FDA / 광고법)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>01번 메인 비주얼</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>UV rays and photoaging account for 80% of the causes of skin aging. Defend with professional-grade protection.</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>UV exposure accounts for up to 80% of visible skin aging signs. Fortify your skin with advanced broad-spectrum defense.</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>단순 노화(aging) 단정을 미국 FDA 기준인 'visible skin aging signs(노화 징후)'로 한정하고, 'professional-grade'를 하이엔드 뷰티 'advanced broad-spectrum defense'로 격상.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>02번 혁신 성분</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>The Logicall Difference</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>The Logically Difference</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>브랜드 식별 철자 오류 (Logicall -&gt; Logically) 정상 교정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>02번 혁신 성분 (AdipoSOL™)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>It restores UV-depleted adiponectin and collagen</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Visibly improves skin elasticity and provides powerful defense against visible signs of photoaging</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>화장품 규정상 금지된 생체 단백질/콜라겐 직접 복원(restores collagen) 클레임을 미용적 탄력 개선 외관(-looking/appearance)으로 안전하게 교정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>02번 혁신 성분 (MelaTrepein™)</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Triggers hormonal shifts that inhibit degradation of melanosomes / By activating autophagy, accelerates melanin breakdown</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Delivers a targeted dual-action solution that visibly diminishes the appearance of stubborn dark spots while preventing future discoloration</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>호르몬 변화(hormonal shifts), 오토파지(autophagy), 멜라닌 분해 등 생체 세포 메커니즘을 배제하고 미용적 외관 개선(diminishes dark spots)으로 우회.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>03번 특장점</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>witl outdoor &amp; urban defense witl outdoor &amp; urban defense with zero white cast</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>outdoor &amp; urban defense with zero white cast</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>치명적인 영문 오탈자('witl') 및 동일 문장 중복 비문 오류 100% 정상화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>04번 3_Point 1</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>highest level of protection against photoaging and deep cellular damage</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>premium broad-spectrum defense against premature photoaging and sun-induced dryness</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>화장품 광고에서 허용되지 않는 'deep cellular damage(깊은 세포 손상)' 주장을 자외선 건조 및 조기 광노화 방어로 교정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>05번 4_Benefit 02</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Photoaging Repair / Anti-Aging &amp; Firming</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Defends Against Visible Signs of Photoaging / Visibly Improves Firmness &amp; Elasticity</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>손상 복구(Repair) 단정 대신 'Defends against signs of photoaging' 및 'Visibly Improves Firmness'로 럭셔리 톤앤매너 안착.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>06번 5_임상 차트</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>MelaTropein?M / Proven to Boost Collagen Production / Clinically Proven Soothing &amp; Anti-Inflammatory Efficacy</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>■ MelaTrepein™ / Clinically Tested to Visibly Improve Skin Firmness / Clinically Tested Soothing &amp; Redness-Relieving Efficacy</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>특수문자 물음표 깨짐(™) 정상화, 콜라겐 생성 단정 배제, 의약품 효능인 'Anti-Inflammatory(항염/소염)'를 'Soothing &amp; Redness-Relieving'으로 완화.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>07번 06_Point 3</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>Absorbs seamlessly for weightless, irritation-free comfort</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Absorbs seamlessly for weightless, breathable comfort with a sweat-resistant, non-greasy finish</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>글로벌 럭셔리 액티브 선케어 규격에 맞춰 통기성(breathable comfort) 및 메이크업 밀착력 강조.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>08번 07_고시정보표</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>일반 비표준 표기 및 단순 직역</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Pretendard 전용 독립 렌더러 기반 표준 INCI 전성분 및 글로벌 Cosmetic Labeling</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>미국 FDA/MoCRA 및 EU 표준 INCI 전성분 1:1 매칭 및 +82 고객센터 번호 완전 표준화.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>